--- a/escola-de-obra/06-curso-inspecao/kit/planilha/planilha-inspecao.xlsx
+++ b/escola-de-obra/06-curso-inspecao/kit/planilha/planilha-inspecao.xlsx
@@ -627,7 +627,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>INSPEÇÃO DE SERVIÇOS CRÍTICOS — uma linha por item verificado (NBR 14931 · 6118 · 15696 · 8545)</t>
+          <t>INSPEÇÃO DE SERVIÇOS CRÍTICOS — uma linha por item verificado (NBR 14931:2023 · 6118 · 15696 · 8545)</t>
         </is>
       </c>
     </row>
